--- a/data/trans_dic/P33B_R1-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R1-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,73; 17,11</t>
+          <t>12,02; 17,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,5; 26,39</t>
+          <t>21,82; 26,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,51; 21,25</t>
+          <t>17,8; 21,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 12,24</t>
+          <t>9,55; 13,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 22,79</t>
+          <t>18,37; 22,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 16,58</t>
+          <t>14,4; 17,32</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,72; 14,01</t>
+          <t>8,49; 13,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 16,6</t>
+          <t>14,98; 19,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 14,19</t>
+          <t>12,08; 15,68</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,75; 17,42</t>
+          <t>12,62; 17,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 23,94</t>
+          <t>21,24; 25,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,15; 20,08</t>
+          <t>17,61; 20,78</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,57; 13,55</t>
+          <t>11,63; 13,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,35; 21,09</t>
+          <t>20,16; 22,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,7; 17,06</t>
+          <t>16,29; 18,02</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91794</t>
+          <t>100222</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>161385</t>
+          <t>177700</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253179</t>
+          <t>277922</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>74419; 108572</t>
+          <t>82927; 119517</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>145118; 178076</t>
+          <t>159751; 196728</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>229292; 278238</t>
+          <t>253031; 304764</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>109568</t>
+          <t>118947</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>197229</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>306798</t>
+          <t>337394</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51786; 146034</t>
+          <t>100209; 139922</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>176332; 218391</t>
+          <t>196664; 243200</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>207514; 356600</t>
+          <t>305194; 367244</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>76236</t>
+          <t>85060</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>115523</t>
+          <t>138787</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>191758</t>
+          <t>223846</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61438; 98710</t>
+          <t>68215; 106216</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57538; 154963</t>
+          <t>121660; 160757</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129060; 232510</t>
+          <t>195183; 253214</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>138645</t>
+          <t>145119</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>231923</t>
+          <t>259059</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>370568</t>
+          <t>404178</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>118145; 161472</t>
+          <t>124961; 168934</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>185205; 261473</t>
+          <t>237460; 287583</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>326131; 405466</t>
+          <t>371169; 437932</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>416243</t>
+          <t>449347</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>706060</t>
+          <t>793993</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1122303</t>
+          <t>1243340</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>331078; 468750</t>
+          <t>410856; 488805</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561591; 771546</t>
+          <t>752721; 835932</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>975390; 1214311</t>
+          <t>1183311; 1308982</t>
         </is>
       </c>
     </row>
